--- a/data/export/2026-10-24-浦东35路.xlsx
+++ b/data/export/2026-10-24-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1492,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1603,1228 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-24-浦东35路.xlsx
+++ b/data/export/2026-10-24-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AC32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>117分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>117.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +812,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -854,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -887,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,33 +931,37 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -965,32 +989,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>117分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -998,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1022,17 +1050,17 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1042,13 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>117.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -1076,32 +1108,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>117分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1109,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1133,33 +1169,37 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>117.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1310,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1421,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1532,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1593,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1643,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1704,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1714,7 +1754,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1815,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1865,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1926,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1976,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2037,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2087,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2148,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2198,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2259,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2309,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2370,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2380,7 +2420,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2481,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2491,7 +2531,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2592,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2602,7 +2642,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2703,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2713,7 +2753,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2814,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2824,7 +2864,1244 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>117.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>1/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>4/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>4/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>117.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>1/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-24-浦东35路.xlsx
+++ b/data/export/2026-10-24-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC32"/>
+  <dimension ref="A1:AC34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -446,10 +446,10 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -999,24 +999,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>117分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>117.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -1118,24 +1118,24 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>117分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>117.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1338,32 +1338,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1371,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1395,33 +1399,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1532,7 +1540,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1593,7 +1601,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1643,7 +1651,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1712,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1754,7 +1762,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1823,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1865,7 +1873,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1893,12 +1901,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq41，推进3站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1926,7 +1934,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1934,10 +1942,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>08:07</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq38（站名待映射） ETA 7分钟参与校验</t>
+        </is>
+      </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -1976,7 +2000,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2061,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2087,7 +2111,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2172,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2198,7 +2222,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2333,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2370,7 +2394,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2420,7 +2444,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2505,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2531,7 +2555,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2616,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2642,7 +2666,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2727,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2753,7 +2777,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2838,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2864,7 +2888,7 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2925,7 +2949,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2975,7 +2999,7 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3060,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3086,7 +3110,7 @@
       <c r="AB23" s="2" t="inlineStr"/>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3147,7 +3171,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3197,7 +3221,7 @@
       <c r="AB24" s="2" t="inlineStr"/>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3282,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3308,7 +3332,7 @@
       <c r="AB25" s="2" t="inlineStr"/>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3393,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3419,7 +3443,7 @@
       <c r="AB26" s="2" t="inlineStr"/>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3504,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3530,7 +3554,7 @@
       <c r="AB27" s="2" t="inlineStr"/>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3591,7 +3615,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3641,7 +3665,7 @@
       <c r="AB28" s="2" t="inlineStr"/>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3702,7 +3726,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3756,7 +3780,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3841,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3871,7 +3895,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -3932,7 +3956,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3986,7 +4010,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -3994,22 +4018,22 @@
       <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4042,12 +4066,12 @@
       <c r="M32" s="2" t="inlineStr"/>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4061,47 +4085,273 @@
       <c r="T32" s="2" t="inlineStr"/>
       <c r="U32" s="2" t="inlineStr">
         <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="V32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W32" s="2" t="inlineStr">
+      <c r="W33" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X32" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y32" s="2" t="inlineStr">
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z32" s="2" t="inlineStr">
+      <c r="Z33" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
+      <c r="AA33" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr">
-        <is>
-          <t>117.0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr">
-        <is>
-          <t>1/27</t>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-24-浦东35路.xlsx
+++ b/data/export/2026-10-24-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC34"/>
+  <dimension ref="A1:AC42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,14 +1065,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
           <t>123.0</t>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -1227,32 +1227,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1260,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1284,33 +1288,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1348,24 +1356,24 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1375,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1424,12 +1432,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1457,32 +1465,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1490,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1514,33 +1526,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -1568,32 +1584,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -1601,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1625,33 +1645,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1751,7 +1775,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1762,7 +1786,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1790,32 +1814,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1823,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1847,33 +1875,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1906,7 +1938,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq41，推进3站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq58，推进20站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1934,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2000,7 +2032,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2028,32 +2060,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -2061,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2085,17 +2121,17 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
@@ -2105,13 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2139,32 +2179,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2172,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2196,33 +2240,37 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2250,12 +2298,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq39推进至seq56，推进17站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2283,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2291,10 +2339,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
       <c r="S16" s="2" t="inlineStr"/>
-      <c r="T16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq23映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
           <t>07:24</t>
@@ -2333,7 +2393,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2444,7 +2504,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2555,7 +2615,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2666,7 +2726,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2727,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2777,7 +2837,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2898,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2888,7 +2948,7 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2949,7 +3009,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2999,7 +3059,7 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3120,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3110,7 +3170,7 @@
       <c r="AB23" s="2" t="inlineStr"/>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3231,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3221,7 +3281,7 @@
       <c r="AB24" s="2" t="inlineStr"/>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3342,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3332,7 +3392,7 @@
       <c r="AB25" s="2" t="inlineStr"/>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3393,7 +3453,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3443,7 +3503,7 @@
       <c r="AB26" s="2" t="inlineStr"/>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3504,7 +3564,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3554,7 +3614,7 @@
       <c r="AB27" s="2" t="inlineStr"/>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3675,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3665,7 +3725,7 @@
       <c r="AB28" s="2" t="inlineStr"/>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3786,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3780,7 +3840,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -3841,7 +3901,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3895,7 +3955,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3956,7 +4016,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4010,7 +4070,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4071,7 +4131,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4121,7 +4181,7 @@
       <c r="AB32" s="2" t="inlineStr"/>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4129,22 +4189,22 @@
       <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4182,7 +4242,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4236,7 +4296,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4244,7 +4304,7 @@
       <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>沪A52272D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -4254,7 +4314,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4297,7 +4357,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4311,47 +4371,959 @@
       <c r="T34" s="2" t="inlineStr"/>
       <c r="U34" s="2" t="inlineStr">
         <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>4/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
           <t>09:15</t>
         </is>
       </c>
-      <c r="V34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W34" s="2" t="inlineStr">
+      <c r="W35" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X34" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y34" s="2" t="inlineStr">
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z34" s="2" t="inlineStr">
+      <c r="Z35" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
+      <c r="AA35" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr">
-        <is>
-          <t>124.0</t>
-        </is>
-      </c>
-      <c r="AC34" s="2" t="inlineStr">
-        <is>
-          <t>4/28</t>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>8/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>10/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-24-浦东35路.xlsx
+++ b/data/export/2026-10-24-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC42"/>
+  <dimension ref="A1:AC50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,14 +2136,14 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>127.0</t>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2532,32 +2532,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2565,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2589,33 +2593,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2643,32 +2651,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -2676,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2700,33 +2712,37 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2754,32 +2770,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2787,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2811,33 +2831,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2937,7 +2961,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2976,32 +3000,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -3009,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3033,33 +3061,37 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3087,32 +3119,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -3120,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3144,33 +3180,37 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3198,32 +3238,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3231,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3255,17 +3299,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3275,13 +3319,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3309,32 +3357,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3342,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3366,17 +3418,17 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3386,13 +3438,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3564,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3675,7 +3731,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3786,7 +3842,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3901,7 +3957,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4016,7 +4072,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4242,7 +4298,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4357,7 +4413,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4472,7 +4528,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4526,7 +4582,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4643,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4641,7 +4697,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4702,7 +4758,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4817,7 +4873,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4932,7 +4988,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5043,7 +5099,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5154,7 +5210,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5208,7 +5264,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5216,22 +5272,22 @@
       <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5264,12 +5320,12 @@
       <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5318,12 +5374,924 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
           <t>129.0</t>
         </is>
       </c>
-      <c r="AC42" s="2" t="inlineStr">
-        <is>
-          <t>10/29</t>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>13/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>17/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr"/>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>18/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>19/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-24-浦东35路.xlsx
+++ b/data/export/2026-10-24-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC50"/>
+  <dimension ref="A1:AC57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3476,32 +3476,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -3509,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3533,33 +3537,37 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3587,32 +3595,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3620,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3644,17 +3656,17 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3664,13 +3676,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3698,32 +3714,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3731,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3755,33 +3775,37 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3881,7 +3905,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3924,32 +3948,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3957,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3981,17 +4009,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -4001,17 +4029,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4039,32 +4067,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4072,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4096,17 +4128,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4116,17 +4148,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4265,32 +4297,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4298,7 +4334,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4322,37 +4358,37 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -4380,32 +4416,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4413,7 +4453,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4437,37 +4477,37 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4495,32 +4535,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4528,7 +4572,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4552,17 +4596,17 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4572,17 +4616,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4610,32 +4654,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4643,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4667,17 +4715,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4687,17 +4735,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4725,32 +4773,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4758,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4782,37 +4834,37 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4840,32 +4892,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -4873,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4897,37 +4953,37 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4955,12 +5011,12 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq50，推进12站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -4988,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4996,10 +5052,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q39" s="2" t="inlineStr"/>
-      <c r="R39" s="2" t="inlineStr"/>
-      <c r="S39" s="2" t="inlineStr"/>
-      <c r="T39" s="2" t="inlineStr"/>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq38（站名待映射） ETA 6分钟参与校验</t>
+        </is>
+      </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
           <t>09:38</t>
@@ -5099,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5210,7 +5282,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5264,7 +5336,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5325,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5379,7 +5451,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5440,7 +5512,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5494,7 +5566,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5555,7 +5627,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5609,7 +5681,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -5670,7 +5742,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5781,7 +5853,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5835,7 +5907,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -5896,7 +5968,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5950,7 +6022,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6083,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6122,7 +6194,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6176,7 +6248,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6309,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6291,7 +6363,812 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>22/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>21/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>17/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>117.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>126.5</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>7/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>128.5</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>8/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-24-浦东35路.xlsx
+++ b/data/export/2026-10-24-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC57"/>
+  <dimension ref="A1:AC62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1780,13 +1780,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1895,17 +1899,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2021,7 +2025,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2097,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,12 +2140,12 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
@@ -2216,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2260,17 +2264,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2382,7 +2386,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2454,7 +2458,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2498,13 +2502,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2577,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2613,17 +2621,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -2688,7 +2696,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2727,22 +2735,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2861,7 +2869,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3037,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3091,7 +3099,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3210,7 +3218,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3329,7 +3337,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3456,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3567,7 +3575,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3694,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3805,7 +3813,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3874,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4039,7 +4047,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4166,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4334,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4453,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4626,7 +4634,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4664,24 +4672,24 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4691,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4740,12 +4748,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -4783,24 +4791,24 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4810,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4859,12 +4867,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4914,12 +4922,12 @@
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4929,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5016,7 +5024,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq50，推进12站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq61，推进23站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -5044,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5099,7 +5107,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5138,32 +5146,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5171,7 +5183,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5195,17 +5207,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5215,13 +5227,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB40" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -5249,32 +5265,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5282,7 +5302,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5306,17 +5326,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5326,17 +5346,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5364,32 +5384,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5397,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5421,27 +5445,27 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
@@ -5479,32 +5503,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5512,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5536,17 +5564,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5556,17 +5584,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -5594,32 +5622,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5627,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5651,17 +5683,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5671,17 +5703,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -5709,32 +5741,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5742,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5766,17 +5802,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5786,13 +5822,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB45" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5820,32 +5860,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -5853,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5877,37 +5921,37 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5968,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6022,7 +6066,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6083,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6194,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6248,7 +6292,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -6309,7 +6353,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6363,7 +6407,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -6424,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6478,7 +6522,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -6539,7 +6583,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6593,7 +6637,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -6654,7 +6698,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6769,7 +6813,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6884,7 +6928,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6999,7 +7043,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7048,12 +7092,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7061,22 +7105,22 @@
       <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A79307D</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -7109,12 +7153,12 @@
       <c r="M57" s="2" t="inlineStr"/>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7128,47 +7172,610 @@
       <c r="T57" s="2" t="inlineStr"/>
       <c r="U57" s="2" t="inlineStr">
         <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="V57" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W57" s="2" t="inlineStr">
+      <c r="W58" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X57" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y57" s="2" t="inlineStr">
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z57" s="2" t="inlineStr">
+      <c r="Z58" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
+      <c r="AA58" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB57" s="2" t="inlineStr">
+      <c r="AB58" s="2" t="inlineStr">
         <is>
           <t>127.0</t>
         </is>
       </c>
-      <c r="AC57" s="2" t="inlineStr">
+      <c r="AC58" s="2" t="inlineStr">
         <is>
           <t>8/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr"/>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>8/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>12/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-24-浦东35路.xlsx
+++ b/data/export/2026-10-24-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC62"/>
+  <dimension ref="A1:AC68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>117.0</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2745,12 +2745,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2859,17 +2859,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2974,13 +2974,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3084,22 +3088,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3203,22 +3207,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3460,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3565,17 +3569,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3698,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3798,22 +3802,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -3874,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3913,17 +3917,17 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>117.0</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4047,7 +4051,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4461,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4500,22 +4504,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4638,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4757,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4872,7 +4876,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4991,7 +4995,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5052,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5356,7 +5360,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5475,7 +5479,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5598,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5817,7 +5821,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5832,7 +5836,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -5870,24 +5874,24 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5897,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5946,12 +5950,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5979,32 +5983,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -6012,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6036,17 +6044,17 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
@@ -6056,17 +6064,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -6094,32 +6102,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -6127,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6151,17 +6163,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6171,13 +6183,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB48" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6205,32 +6221,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -6238,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6262,37 +6282,37 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6320,32 +6340,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -6353,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6377,37 +6401,37 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -6435,32 +6459,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -6468,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6492,17 +6520,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6512,17 +6540,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6550,32 +6578,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6583,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6607,37 +6639,37 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -6665,32 +6697,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6698,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6722,32 +6758,32 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>117.0</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6780,32 +6816,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6813,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6837,37 +6877,37 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6928,7 +6968,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7043,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7097,7 +7137,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7158,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7269,7 +7309,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7323,7 +7363,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7384,7 +7424,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7495,7 +7535,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7549,7 +7589,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7610,7 +7650,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7721,7 +7761,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7770,12 +7810,702 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>15/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>19/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
           <t>128.0</t>
         </is>
       </c>
-      <c r="AC62" s="2" t="inlineStr">
-        <is>
-          <t>12/29</t>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>13/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>22/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>121.5</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>132.5</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>20/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>127.3</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>10/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-24-浦东35路.xlsx
+++ b/data/export/2026-10-24-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC68"/>
+  <dimension ref="A1:AC70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -6588,24 +6588,24 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6664,12 +6664,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6826,12 +6826,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6935,32 +6935,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6968,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6992,17 +6996,17 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -7012,12 +7016,12 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7083,7 +7087,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7122,7 +7126,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7137,7 +7141,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7309,7 +7313,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7424,7 +7428,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7535,7 +7539,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7650,7 +7654,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7761,7 +7765,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7876,7 +7880,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7991,7 +7995,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8045,7 +8049,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -8106,7 +8110,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8160,7 +8164,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -8221,7 +8225,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8336,7 +8340,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8385,12 +8389,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -8398,22 +8402,22 @@
       <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -8451,7 +8455,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8465,45 +8469,275 @@
       <c r="T68" s="2" t="inlineStr"/>
       <c r="U68" s="2" t="inlineStr">
         <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>18/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
           <t>14:35</t>
         </is>
       </c>
-      <c r="V68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W68" s="2" t="inlineStr">
+      <c r="W69" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X68" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y68" s="2" t="inlineStr">
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z68" s="2" t="inlineStr">
+      <c r="Z69" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
+      <c r="AA69" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB68" s="2" t="inlineStr">
-        <is>
-          <t>127.3</t>
-        </is>
-      </c>
-      <c r="AC68" s="2" t="inlineStr">
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>12/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>127.5</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
         <is>
           <t>10/29</t>
         </is>

--- a/data/export/2026-10-24-浦东35路.xlsx
+++ b/data/export/2026-10-24-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC70"/>
+  <dimension ref="A1:AC73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>125.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,14 +1422,14 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>134.5</t>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,14 +1894,14 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>127.5</t>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2025,18 +2025,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2155,7 +2159,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2458,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2512,7 +2516,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2635,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2869,7 +2873,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2988,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3053,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3103,7 +3107,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3172,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3341,7 +3345,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3583,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3702,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3767,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3817,7 +3821,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3997,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4051,7 +4055,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4174,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4395,12 +4399,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>125.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4469,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4514,12 +4518,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4638,7 +4642,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4742,14 +4746,14 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
           <t>134.5</t>
@@ -4757,7 +4761,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4866,17 +4870,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4945,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4995,7 +4999,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5241,7 +5245,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5345,14 +5349,14 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
           <t>127.5</t>
@@ -5360,7 +5364,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5479,7 +5483,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5717,7 +5721,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5836,7 +5840,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6074,7 +6078,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -6193,7 +6197,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6262,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6377,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6431,7 +6435,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -6550,7 +6554,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6619,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6669,7 +6673,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6738,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6826,24 +6830,24 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6853,7 +6857,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6902,12 +6906,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6945,24 +6949,24 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6972,7 +6976,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7021,12 +7025,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>125.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -7054,32 +7058,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -7087,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7111,17 +7119,17 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7131,17 +7139,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -7169,12 +7177,12 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq39推进至seq54，推进15站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -7202,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7210,10 +7218,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q57" s="2" t="inlineStr"/>
-      <c r="R57" s="2" t="inlineStr"/>
-      <c r="S57" s="2" t="inlineStr"/>
-      <c r="T57" s="2" t="inlineStr"/>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="T57" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq23映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq39（站名待映射） ETA 4分钟参与校验</t>
+        </is>
+      </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
           <t>12:28</t>
@@ -7313,7 +7337,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7367,7 +7391,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -7395,32 +7419,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7428,7 +7456,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7452,33 +7480,37 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB59" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -7539,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7593,7 +7625,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7765,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7880,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7934,7 +7966,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -7995,7 +8027,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8110,7 +8142,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8164,7 +8196,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -8225,7 +8257,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8340,7 +8372,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8394,7 +8426,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -8455,7 +8487,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8509,7 +8541,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -8570,7 +8602,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8619,12 +8651,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -8632,22 +8664,22 @@
       <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A52272D</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8680,12 +8712,12 @@
       <c r="M70" s="2" t="inlineStr"/>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8699,47 +8731,392 @@
       <c r="T70" s="2" t="inlineStr"/>
       <c r="U70" s="2" t="inlineStr">
         <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>134.5</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>25/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="V70" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W70" s="2" t="inlineStr">
+      <c r="W71" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X70" s="2" t="inlineStr">
+      <c r="X71" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y70" s="2" t="inlineStr">
+      <c r="Y71" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z70" s="2" t="inlineStr">
+      <c r="Z71" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>130.7</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>17/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB70" s="2" t="inlineStr">
+      <c r="AB72" s="2" t="inlineStr">
         <is>
           <t>127.5</t>
         </is>
       </c>
-      <c r="AC70" s="2" t="inlineStr">
-        <is>
-          <t>10/29</t>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-24-浦东35路.xlsx
+++ b/data/export/2026-10-24-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC73"/>
+  <dimension ref="A1:AC78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2149,17 +2149,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2263,14 +2263,14 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
           <t>129.5</t>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2395,13 +2395,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2506,17 +2510,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2744,17 +2748,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>130.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2858,7 +2862,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -3053,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3172,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3216,17 +3220,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3330,7 +3334,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3464,7 +3468,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3687,7 +3691,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3767,7 +3771,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3882,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4001,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4469,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4523,7 +4527,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4826,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4875,12 +4879,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4989,17 +4993,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5115,7 +5119,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5310,7 +5314,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5429,7 +5433,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5473,17 +5477,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5552,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5587,14 +5591,14 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
           <t>129.5</t>
@@ -5602,7 +5606,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5790,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5830,17 +5834,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -5905,7 +5909,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5949,17 +5953,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>130.3</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6024,7 +6028,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6063,7 +6067,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6262,7 +6266,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6306,17 +6310,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6385,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6619,7 +6623,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6738,7 +6742,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6857,7 +6861,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6911,7 +6915,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -7068,24 +7072,24 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -7095,7 +7099,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7144,12 +7148,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -7182,7 +7186,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq39推进至seq54，推进15站，达到≥2站确认条件</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq39推进至seq59，推进20站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -7210,7 +7214,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7265,7 +7269,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7304,32 +7308,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -7337,7 +7345,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7361,17 +7369,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7381,17 +7389,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -7429,24 +7437,24 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7456,7 +7464,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7505,7 +7513,7 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7538,32 +7546,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7571,7 +7583,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7595,17 +7607,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7615,17 +7627,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -7653,32 +7665,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -7686,7 +7702,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7710,17 +7726,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7730,13 +7746,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB61" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -7764,32 +7784,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -7797,7 +7821,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7821,17 +7845,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7841,17 +7865,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>130.3</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -7879,32 +7903,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -7912,7 +7940,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7936,17 +7964,17 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7956,17 +7984,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -7994,32 +8022,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -8027,7 +8059,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8051,17 +8083,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8071,17 +8103,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -8142,7 +8174,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8257,7 +8289,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8372,7 +8404,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8487,7 +8519,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8602,7 +8634,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8656,7 +8688,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -8717,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8832,7 +8864,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8881,12 +8913,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -8947,7 +8979,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9009,22 +9041,22 @@
       <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A79307D</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9057,12 +9089,12 @@
       <c r="M73" s="2" t="inlineStr"/>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9076,47 +9108,618 @@
       <c r="T73" s="2" t="inlineStr"/>
       <c r="U73" s="2" t="inlineStr">
         <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr"/>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
           <t>15:25</t>
         </is>
       </c>
-      <c r="V73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W73" s="2" t="inlineStr">
+      <c r="W74" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X73" s="2" t="inlineStr">
+      <c r="X74" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y73" s="2" t="inlineStr">
+      <c r="Y74" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z73" s="2" t="inlineStr">
+      <c r="Z74" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
+      <c r="AA74" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB73" s="2" t="inlineStr">
-        <is>
-          <t>124.0</t>
-        </is>
-      </c>
-      <c r="AC73" s="2" t="inlineStr">
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
         <is>
           <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>129.5</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>15/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>5/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>22/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>134.5</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>25/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-24-浦东35路.xlsx
+++ b/data/export/2026-10-24-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC78"/>
+  <dimension ref="A1:AC85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,14 +1303,14 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>132.5</t>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3101,17 +3101,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3225,12 +3225,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -3771,7 +3771,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3815,17 +3815,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4049,17 +4049,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4631,14 +4631,14 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
           <t>132.5</t>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4755,17 +4755,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6429,17 +6429,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6667,17 +6667,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -6742,7 +6742,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6905,12 +6905,12 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6980,7 +6980,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7925,12 +7925,12 @@
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7940,7 +7940,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8032,24 +8032,24 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8059,7 +8059,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8108,12 +8108,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -8141,32 +8141,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -8174,7 +8178,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8198,17 +8202,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8218,17 +8222,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -8289,7 +8293,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8371,32 +8375,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8404,7 +8412,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8428,17 +8436,17 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8448,17 +8456,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -8486,32 +8494,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8519,7 +8531,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8543,17 +8555,17 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
@@ -8563,17 +8575,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -8601,32 +8613,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8634,7 +8650,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8658,17 +8674,17 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
@@ -8678,12 +8694,12 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8716,32 +8732,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8749,7 +8769,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8773,17 +8793,17 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
@@ -8793,17 +8813,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8884,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8979,7 +8999,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9033,7 +9053,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9114,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9205,7 +9225,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9320,7 +9340,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9435,7 +9455,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9550,7 +9570,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9604,7 +9624,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9685,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9719,7 +9739,812 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>8/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>18/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>125.5</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>4/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>125.3</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>3/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>132.5</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>22/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>5/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>13/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-24-浦东35路.xlsx
+++ b/data/export/2026-10-24-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC85"/>
+  <dimension ref="A1:AC93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3215,7 +3215,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4044,22 +4044,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4750,22 +4750,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6082,7 +6082,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6305,7 +6305,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -6861,7 +6861,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6980,7 +6980,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7143,12 +7143,12 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7583,7 +7583,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7622,7 +7622,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8098,7 +8098,7 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -8504,24 +8504,24 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8531,7 +8531,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8570,22 +8570,22 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -8635,12 +8635,12 @@
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8650,7 +8650,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8742,24 +8742,24 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8808,22 +8808,22 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -8851,32 +8851,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -8884,7 +8888,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8908,17 +8912,17 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
@@ -8928,12 +8932,12 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8999,7 +9003,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9081,12 +9085,12 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程31%处后消失；随后反向物理轨迹由seq38推进至seq56，推进18站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -9114,7 +9118,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9122,10 +9126,18 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>沪南路华夏西路</t>
+        </is>
+      </c>
       <c r="R73" s="2" t="inlineStr"/>
       <c r="S73" s="2" t="inlineStr"/>
-      <c r="T73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq21映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U73" s="2" t="inlineStr">
         <is>
           <t>15:22</t>
@@ -9225,7 +9237,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9264,7 +9276,7 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9340,7 +9352,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9455,7 +9467,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9570,7 +9582,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9624,7 +9636,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -9685,7 +9697,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9739,7 +9751,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -9800,7 +9812,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9915,7 +9927,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10030,7 +10042,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10145,7 +10157,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10260,7 +10272,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10314,7 +10326,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -10375,7 +10387,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10490,7 +10502,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10548,6 +10560,926 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>127.7</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>133.3</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>23/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>130.3</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>17/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>5/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>127.7</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>136.0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>27/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>8/29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-24-浦东35路.xlsx
+++ b/data/export/2026-10-24-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC93"/>
+  <dimension ref="A1:AC100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2030,17 +2030,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2395,17 +2395,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2867,17 +2867,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3334,22 +3334,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3572,22 +3572,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3691,22 +3691,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5596,17 +5596,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -5909,7 +5909,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6072,17 +6072,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6543,22 +6543,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6915,7 +6915,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -7153,7 +7153,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7269,7 +7269,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7508,17 +7508,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7746,17 +7746,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7979,7 +7979,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -8531,7 +8531,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8585,7 +8585,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -8769,7 +8769,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8823,7 +8823,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9204,32 +9204,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -9237,7 +9241,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9261,17 +9265,17 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
@@ -9281,17 +9285,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -9319,32 +9323,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9352,7 +9360,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9376,17 +9384,17 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
@@ -9396,17 +9404,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -9434,32 +9442,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9467,7 +9479,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9491,37 +9503,37 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -9549,32 +9561,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9582,7 +9598,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9606,37 +9622,37 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA77" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -9664,32 +9680,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>164分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -9697,7 +9717,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9721,17 +9741,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9741,17 +9761,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -9779,32 +9799,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9812,7 +9836,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9836,17 +9860,17 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
@@ -9856,17 +9880,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -9894,32 +9918,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9927,7 +9955,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9951,37 +9979,37 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA80" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -10042,7 +10070,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10081,7 +10109,7 @@
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
@@ -10096,7 +10124,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -10157,7 +10185,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10211,7 +10239,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -10272,7 +10300,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10326,7 +10354,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -10387,7 +10415,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10441,7 +10469,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -10502,7 +10530,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10556,7 +10584,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -10617,7 +10645,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10671,7 +10699,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -10732,7 +10760,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10786,7 +10814,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -10847,7 +10875,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10901,7 +10929,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -10962,7 +10990,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11016,7 +11044,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -11077,7 +11105,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11131,7 +11159,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -11192,7 +11220,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11246,7 +11274,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -11307,7 +11335,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11351,17 +11379,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -11369,22 +11397,22 @@
       <c r="A93" s="2" t="inlineStr"/>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A79307D</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>18:20</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -11417,12 +11445,12 @@
       <c r="M93" s="2" t="inlineStr"/>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11436,47 +11464,848 @@
       <c r="T93" s="2" t="inlineStr"/>
       <c r="U93" s="2" t="inlineStr">
         <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr"/>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
           <t>18:20</t>
         </is>
       </c>
-      <c r="V93" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W93" s="2" t="inlineStr">
+      <c r="W94" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X93" s="2" t="inlineStr">
+      <c r="X94" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y93" s="2" t="inlineStr">
+      <c r="Y94" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z93" s="2" t="inlineStr">
+      <c r="Z94" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA93" s="2" t="inlineStr">
+      <c r="AA94" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB93" s="2" t="inlineStr">
+      <c r="AB94" s="2" t="inlineStr">
         <is>
           <t>127.0</t>
         </is>
       </c>
-      <c r="AC93" s="2" t="inlineStr">
-        <is>
-          <t>8/29</t>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>129.5</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>13/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>135.5</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>23/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>132.5</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>17/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>127.5</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>7/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>137.7</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>26/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>125.5</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>3/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-24-浦东35路.xlsx
+++ b/data/export/2026-10-24-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC100"/>
+  <dimension ref="A1:AC101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4168,17 +4168,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6077,7 +6077,7 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6553,12 +6553,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7153,7 +7153,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7940,7 +7940,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8059,7 +8059,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -8531,7 +8531,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8585,7 +8585,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -8769,7 +8769,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9652,7 +9652,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -9690,24 +9690,24 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>164分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9809,24 +9809,24 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9836,7 +9836,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9875,7 +9875,7 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9885,12 +9885,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -9928,24 +9928,24 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>151分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9955,7 +9955,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10004,12 +10004,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -10037,32 +10037,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10070,7 +10074,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10094,17 +10098,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10114,17 +10118,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -10185,7 +10189,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10300,7 +10304,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10354,7 +10358,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -10415,7 +10419,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10469,7 +10473,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -10530,7 +10534,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10584,7 +10588,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -10645,7 +10649,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10699,7 +10703,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -10760,7 +10764,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10814,7 +10818,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -10875,7 +10879,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10990,7 +10994,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11044,7 +11048,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -11105,7 +11109,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11159,7 +11163,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -11220,7 +11224,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11335,7 +11339,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11389,7 +11393,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -11450,7 +11454,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11561,7 +11565,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11615,7 +11619,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -11676,7 +11680,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11791,7 +11795,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11906,7 +11910,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11960,7 +11964,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -12021,7 +12025,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12075,7 +12079,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -12136,7 +12140,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12185,12 +12189,12 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -12251,7 +12255,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12295,17 +12299,132 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>10/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB100" s="2" t="inlineStr">
-        <is>
-          <t>125.5</t>
-        </is>
-      </c>
-      <c r="AC100" s="2" t="inlineStr">
-        <is>
-          <t>3/29</t>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>25/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-24-浦东35路.xlsx
+++ b/data/export/2026-10-24-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC101"/>
+  <dimension ref="A1:AC106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>125.3</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,12 +1665,12 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,22 +1775,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4049,17 +4049,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4398,17 +4398,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>125.3</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4993,12 +4993,12 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5234,22 +5234,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6424,7 +6424,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7024,17 +7024,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>125.3</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7940,7 +7940,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8059,7 +8059,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
@@ -8531,7 +8531,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8575,17 +8575,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -8769,7 +8769,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -9118,7 +9118,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -9360,7 +9360,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9533,7 +9533,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9836,7 +9836,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9955,7 +9955,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10128,7 +10128,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -10156,32 +10156,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10189,7 +10193,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10213,17 +10217,17 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
@@ -10233,17 +10237,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>125.3</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -10304,7 +10308,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10343,7 +10347,7 @@
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
@@ -10386,32 +10390,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10419,7 +10427,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10443,37 +10451,37 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -10501,32 +10509,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -10534,7 +10546,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10558,17 +10570,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10578,12 +10590,12 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
@@ -10649,7 +10661,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10703,7 +10715,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -10731,32 +10743,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10764,7 +10780,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10788,17 +10804,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10808,17 +10824,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -10879,7 +10895,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10994,7 +11010,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11048,7 +11064,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -11109,7 +11125,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11163,7 +11179,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -11224,7 +11240,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11339,7 +11355,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11393,7 +11409,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -11454,7 +11470,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11565,7 +11581,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11619,7 +11635,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -11680,7 +11696,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11734,7 +11750,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -11795,7 +11811,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11910,7 +11926,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12025,7 +12041,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12079,7 +12095,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -12140,7 +12156,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12255,7 +12271,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12309,7 +12325,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -12317,22 +12333,22 @@
       <c r="A101" s="2" t="inlineStr"/>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -12365,12 +12381,12 @@
       <c r="M101" s="2" t="inlineStr"/>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12384,47 +12400,622 @@
       <c r="T101" s="2" t="inlineStr"/>
       <c r="U101" s="2" t="inlineStr">
         <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>25/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="V101" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W101" s="2" t="inlineStr">
+      <c r="W102" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X101" s="2" t="inlineStr">
+      <c r="X102" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y101" s="2" t="inlineStr">
+      <c r="Y102" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z101" s="2" t="inlineStr">
+      <c r="Z102" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA101" s="2" t="inlineStr">
+      <c r="AA102" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB101" s="2" t="inlineStr">
+      <c r="AB102" s="2" t="inlineStr">
         <is>
           <t>137.0</t>
         </is>
       </c>
-      <c r="AC101" s="2" t="inlineStr">
+      <c r="AC102" s="2" t="inlineStr">
         <is>
           <t>25/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>132.5</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>18/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>140.3</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>27/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>133.3</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>21/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>129.5</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>12/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-24-浦东35路.xlsx
+++ b/data/export/2026-10-24-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC106"/>
+  <dimension ref="A1:AC108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2624,22 +2624,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>130.3</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3220,17 +3220,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3339,17 +3339,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4755,17 +4755,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5710,22 +5710,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>130.3</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6310,17 +6310,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7702,7 +7702,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>130.3</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7940,7 +7940,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8059,7 +8059,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8103,17 +8103,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8531,7 +8531,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8813,17 +8813,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9118,7 +9118,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9836,7 +9836,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9955,7 +9955,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10074,7 +10074,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10128,7 +10128,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -10247,7 +10247,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10427,7 +10427,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10753,24 +10753,24 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -10780,7 +10780,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
@@ -10862,32 +10862,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -10895,7 +10899,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10919,17 +10923,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10939,12 +10943,12 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>130.3</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -10977,32 +10981,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -11010,7 +11018,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11034,37 +11042,37 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA89" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -11092,32 +11100,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -11125,7 +11137,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11149,17 +11161,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11169,17 +11181,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>127.7</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -11207,32 +11219,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11240,7 +11256,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11264,17 +11280,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11284,17 +11300,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -11355,7 +11371,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11437,12 +11453,12 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程28%处后消失；随后反向物理轨迹由seq38推进至seq62，推进24站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -11470,7 +11486,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11478,10 +11494,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q93" s="2" t="inlineStr"/>
-      <c r="R93" s="2" t="inlineStr"/>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>物理seq19（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
       <c r="S93" s="2" t="inlineStr"/>
-      <c r="T93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq19映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U93" s="2" t="inlineStr">
         <is>
           <t>18:12</t>
@@ -11581,7 +11609,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11620,7 +11648,7 @@
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
@@ -11635,7 +11663,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -11663,32 +11691,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11696,7 +11728,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11720,17 +11752,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11740,17 +11772,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -11811,7 +11843,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11926,7 +11958,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12041,7 +12073,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12123,12 +12155,12 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq30，推进2站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -12156,7 +12188,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12164,10 +12196,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q99" s="2" t="inlineStr"/>
-      <c r="R99" s="2" t="inlineStr"/>
-      <c r="S99" s="2" t="inlineStr"/>
-      <c r="T99" s="2" t="inlineStr"/>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>物理seq32（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr">
+        <is>
+          <t>20:02</t>
+        </is>
+      </c>
+      <c r="S99" s="2" t="inlineStr">
+        <is>
+          <t>20:07</t>
+        </is>
+      </c>
+      <c r="T99" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U99" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -12271,7 +12319,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12325,7 +12373,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -12386,7 +12434,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12501,7 +12549,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12616,7 +12664,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12731,7 +12779,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12846,7 +12894,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12961,7 +13009,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13019,6 +13067,236 @@
         </is>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr"/>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr"/>
+      <c r="R107" s="2" t="inlineStr"/>
+      <c r="S107" s="2" t="inlineStr"/>
+      <c r="T107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z107" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA107" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB107" s="2" t="inlineStr">
+        <is>
+          <t>127.3</t>
+        </is>
+      </c>
+      <c r="AC107" s="2" t="inlineStr">
+        <is>
+          <t>4/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr"/>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr"/>
+      <c r="R108" s="2" t="inlineStr"/>
+      <c r="S108" s="2" t="inlineStr"/>
+      <c r="T108" s="2" t="inlineStr"/>
+      <c r="U108" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V108" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W108" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y108" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z108" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA108" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB108" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC108" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-24-浦东35路.xlsx
+++ b/data/export/2026-10-24-浦东35路.xlsx
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1899,17 +1899,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2268,17 +2268,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2510,17 +2510,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2758,7 +2758,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2867,17 +2867,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3696,17 +3696,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4168,17 +4168,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5358,17 +5358,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5596,17 +5596,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5834,17 +5834,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6072,17 +6072,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6147,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -7153,7 +7153,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7984,17 +7984,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -8113,7 +8113,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -8823,7 +8823,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9047,17 +9047,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -9295,7 +9295,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -9360,7 +9360,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9404,17 +9404,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9642,17 +9642,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -9717,7 +9717,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9761,17 +9761,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -9836,7 +9836,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9955,7 +9955,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10009,7 +10009,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -10074,7 +10074,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10118,17 +10118,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -10427,7 +10427,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -10715,7 +10715,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11072,7 +11072,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11191,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -11310,7 +11310,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -11425,7 +11425,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11701,24 +11701,24 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -11728,7 +11728,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11777,7 +11777,7 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
@@ -11810,32 +11810,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -11843,7 +11847,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11867,17 +11871,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11887,17 +11891,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -11925,32 +11929,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11958,7 +11966,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11982,17 +11990,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -12002,17 +12010,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -12040,32 +12048,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -12073,7 +12085,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12097,17 +12109,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12117,17 +12129,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -12160,7 +12172,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq30，推进2站，达到≥2站确认条件</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq59，推进31站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -12188,7 +12200,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12258,7 +12270,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -12286,32 +12298,36 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12319,7 +12335,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12343,17 +12359,17 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
@@ -12363,17 +12379,17 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -12401,32 +12417,36 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -12434,7 +12454,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12458,17 +12478,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12478,17 +12498,17 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>135.2</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -12549,7 +12569,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12664,7 +12684,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12718,7 +12738,7 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -12746,32 +12766,36 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M104" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -12779,7 +12803,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12803,17 +12827,17 @@
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y104" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z104" s="2" t="inlineStr">
@@ -12823,17 +12847,17 @@
       </c>
       <c r="AA104" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>137.8</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -12894,7 +12918,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -13009,7 +13033,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13063,7 +13087,7 @@
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -13124,7 +13148,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13178,7 +13202,7 @@
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -13239,7 +13263,7 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">

--- a/data/export/2026-10-24-浦东35路.xlsx
+++ b/data/export/2026-10-24-浦东35路.xlsx
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3101,17 +3101,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>131.2</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5239,17 +5239,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -5368,7 +5368,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6385,7 +6385,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6429,17 +6429,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>131.2</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6558,7 +6558,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -6915,7 +6915,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -7153,7 +7153,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8222,17 +8222,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>131.2</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -9057,7 +9057,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -9295,7 +9295,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -9533,7 +9533,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -9652,7 +9652,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -9717,7 +9717,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -10009,7 +10009,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -10128,7 +10128,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -10247,7 +10247,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -10362,7 +10362,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -10427,7 +10427,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10471,17 +10471,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -10715,7 +10715,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11072,7 +11072,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -11425,7 +11425,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11663,7 +11663,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -11782,7 +11782,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -12020,7 +12020,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -12139,7 +12139,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -12270,7 +12270,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -12389,7 +12389,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -12738,7 +12738,7 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -12803,7 +12803,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12885,32 +12885,36 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:05</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M105" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -12918,7 +12922,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12942,17 +12946,17 @@
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y105" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z105" s="2" t="inlineStr">
@@ -12962,17 +12966,17 @@
       </c>
       <c r="AA105" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>131.2</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -13000,32 +13004,36 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:04</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>119分钟</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M106" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -13033,7 +13041,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13057,17 +13065,17 @@
       </c>
       <c r="W106" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X106" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y106" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z106" s="2" t="inlineStr">
@@ -13077,17 +13085,17 @@
       </c>
       <c r="AA106" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -13148,7 +13156,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13202,7 +13210,7 @@
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -13263,7 +13271,7 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
@@ -13317,7 +13325,7 @@
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
